--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609139</v>
+        <v>122609130</v>
       </c>
       <c r="B2" t="n">
-        <v>90839</v>
+        <v>91277</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521067</v>
+        <v>521075</v>
       </c>
       <c r="R2" t="n">
-        <v>6704010</v>
+        <v>6704005</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609145</v>
+        <v>122609113</v>
       </c>
       <c r="B3" t="n">
-        <v>90839</v>
+        <v>91277</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521191</v>
+        <v>521081</v>
       </c>
       <c r="R3" t="n">
-        <v>6703848</v>
+        <v>6704102</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609151</v>
+        <v>122609047</v>
       </c>
       <c r="B4" t="n">
-        <v>100503</v>
+        <v>90839</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,35 +899,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521159</v>
+        <v>520920</v>
       </c>
       <c r="R4" t="n">
-        <v>6703836</v>
+        <v>6704243</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -998,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609097</v>
+        <v>122609122</v>
       </c>
       <c r="B5" t="n">
         <v>90839</v>
@@ -1041,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521009</v>
+        <v>521065</v>
       </c>
       <c r="R5" t="n">
-        <v>6704113</v>
+        <v>6704125</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1104,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609047</v>
+        <v>122609139</v>
       </c>
       <c r="B6" t="n">
         <v>90839</v>
@@ -1147,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520920</v>
+        <v>521067</v>
       </c>
       <c r="R6" t="n">
-        <v>6704243</v>
+        <v>6704010</v>
       </c>
       <c r="S6" t="n">
         <v>75</v>
@@ -1210,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609122</v>
+        <v>122609123</v>
       </c>
       <c r="B7" t="n">
         <v>90839</v>
@@ -1253,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521065</v>
+        <v>521094</v>
       </c>
       <c r="R7" t="n">
-        <v>6704125</v>
+        <v>6704095</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609130</v>
+        <v>122609145</v>
       </c>
       <c r="B8" t="n">
-        <v>91277</v>
+        <v>90839</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521075</v>
+        <v>521191</v>
       </c>
       <c r="R8" t="n">
-        <v>6704005</v>
+        <v>6703848</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1422,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609123</v>
+        <v>122609097</v>
       </c>
       <c r="B9" t="n">
         <v>90839</v>
@@ -1465,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521094</v>
+        <v>521009</v>
       </c>
       <c r="R9" t="n">
-        <v>6704095</v>
+        <v>6704113</v>
       </c>
       <c r="S9" t="n">
         <v>75</v>
@@ -1528,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609113</v>
+        <v>122609151</v>
       </c>
       <c r="B10" t="n">
-        <v>91277</v>
+        <v>100503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,30 +1535,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521081</v>
+        <v>521159</v>
       </c>
       <c r="R10" t="n">
-        <v>6704102</v>
+        <v>6703836</v>
       </c>
       <c r="S10" t="n">
         <v>75</v>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609130</v>
+        <v>122609113</v>
       </c>
       <c r="B2" t="n">
         <v>91277</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521075</v>
+        <v>521081</v>
       </c>
       <c r="R2" t="n">
-        <v>6704005</v>
+        <v>6704102</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609113</v>
+        <v>122609130</v>
       </c>
       <c r="B3" t="n">
         <v>91277</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521081</v>
+        <v>521075</v>
       </c>
       <c r="R3" t="n">
-        <v>6704102</v>
+        <v>6704005</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609113</v>
+        <v>122609151</v>
       </c>
       <c r="B2" t="n">
-        <v>91277</v>
+        <v>100506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521081</v>
+        <v>521159</v>
       </c>
       <c r="R2" t="n">
-        <v>6704102</v>
+        <v>6703836</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609130</v>
+        <v>122609122</v>
       </c>
       <c r="B3" t="n">
-        <v>91277</v>
+        <v>90833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521075</v>
+        <v>521065</v>
       </c>
       <c r="R3" t="n">
-        <v>6704005</v>
+        <v>6704125</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609047</v>
+        <v>122609113</v>
       </c>
       <c r="B4" t="n">
-        <v>90839</v>
+        <v>91278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520920</v>
+        <v>521081</v>
       </c>
       <c r="R4" t="n">
-        <v>6704243</v>
+        <v>6704102</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609122</v>
+        <v>122609123</v>
       </c>
       <c r="B5" t="n">
-        <v>90839</v>
+        <v>90833</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521065</v>
+        <v>521094</v>
       </c>
       <c r="R5" t="n">
-        <v>6704125</v>
+        <v>6704095</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609139</v>
+        <v>122609145</v>
       </c>
       <c r="B6" t="n">
-        <v>90839</v>
+        <v>90833</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521067</v>
+        <v>521191</v>
       </c>
       <c r="R6" t="n">
-        <v>6704010</v>
+        <v>6703848</v>
       </c>
       <c r="S6" t="n">
         <v>75</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609123</v>
+        <v>122609047</v>
       </c>
       <c r="B7" t="n">
-        <v>90839</v>
+        <v>90833</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521094</v>
+        <v>520920</v>
       </c>
       <c r="R7" t="n">
-        <v>6704095</v>
+        <v>6704243</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609145</v>
+        <v>122609139</v>
       </c>
       <c r="B8" t="n">
-        <v>90839</v>
+        <v>90833</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521191</v>
+        <v>521067</v>
       </c>
       <c r="R8" t="n">
-        <v>6703848</v>
+        <v>6704010</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1420,7 +1425,7 @@
         <v>122609097</v>
       </c>
       <c r="B9" t="n">
-        <v>90839</v>
+        <v>90833</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609151</v>
+        <v>122609130</v>
       </c>
       <c r="B10" t="n">
-        <v>100503</v>
+        <v>91278</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,35 +1540,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521159</v>
+        <v>521075</v>
       </c>
       <c r="R10" t="n">
-        <v>6703836</v>
+        <v>6704005</v>
       </c>
       <c r="S10" t="n">
         <v>75</v>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609151</v>
+        <v>122609139</v>
       </c>
       <c r="B2" t="n">
-        <v>100506</v>
+        <v>90833</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521159</v>
+        <v>521067</v>
       </c>
       <c r="R2" t="n">
-        <v>6703836</v>
+        <v>6704010</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -786,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609122</v>
+        <v>122609123</v>
       </c>
       <c r="B3" t="n">
         <v>90833</v>
@@ -829,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521065</v>
+        <v>521094</v>
       </c>
       <c r="R3" t="n">
-        <v>6704125</v>
+        <v>6704095</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609113</v>
+        <v>122609047</v>
       </c>
       <c r="B4" t="n">
-        <v>91278</v>
+        <v>90833</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521081</v>
+        <v>520920</v>
       </c>
       <c r="R4" t="n">
-        <v>6704102</v>
+        <v>6704243</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -998,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609123</v>
+        <v>122609097</v>
       </c>
       <c r="B5" t="n">
         <v>90833</v>
@@ -1041,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521094</v>
+        <v>521009</v>
       </c>
       <c r="R5" t="n">
-        <v>6704095</v>
+        <v>6704113</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609145</v>
+        <v>122609151</v>
       </c>
       <c r="B6" t="n">
-        <v>90833</v>
+        <v>100506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,30 +1111,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521191</v>
+        <v>521159</v>
       </c>
       <c r="R6" t="n">
-        <v>6703848</v>
+        <v>6703836</v>
       </c>
       <c r="S6" t="n">
         <v>75</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609047</v>
+        <v>122609122</v>
       </c>
       <c r="B7" t="n">
         <v>90833</v>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520920</v>
+        <v>521065</v>
       </c>
       <c r="R7" t="n">
-        <v>6704243</v>
+        <v>6704125</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609139</v>
+        <v>122609113</v>
       </c>
       <c r="B8" t="n">
-        <v>90833</v>
+        <v>91278</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521067</v>
+        <v>521081</v>
       </c>
       <c r="R8" t="n">
-        <v>6704010</v>
+        <v>6704102</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609097</v>
+        <v>122609130</v>
       </c>
       <c r="B9" t="n">
-        <v>90833</v>
+        <v>91278</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521009</v>
+        <v>521075</v>
       </c>
       <c r="R9" t="n">
-        <v>6704113</v>
+        <v>6704005</v>
       </c>
       <c r="S9" t="n">
         <v>75</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609130</v>
+        <v>122609145</v>
       </c>
       <c r="B10" t="n">
-        <v>91278</v>
+        <v>90833</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521075</v>
+        <v>521191</v>
       </c>
       <c r="R10" t="n">
-        <v>6704005</v>
+        <v>6703848</v>
       </c>
       <c r="S10" t="n">
         <v>75</v>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609139</v>
+        <v>122609047</v>
       </c>
       <c r="B2" t="n">
-        <v>90833</v>
+        <v>90834</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521067</v>
+        <v>520920</v>
       </c>
       <c r="R2" t="n">
-        <v>6704010</v>
+        <v>6704243</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609123</v>
+        <v>122609113</v>
       </c>
       <c r="B3" t="n">
-        <v>90833</v>
+        <v>91279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521094</v>
+        <v>521081</v>
       </c>
       <c r="R3" t="n">
-        <v>6704095</v>
+        <v>6704102</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609047</v>
+        <v>122609123</v>
       </c>
       <c r="B4" t="n">
-        <v>90833</v>
+        <v>90834</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520920</v>
+        <v>521094</v>
       </c>
       <c r="R4" t="n">
-        <v>6704243</v>
+        <v>6704095</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609097</v>
+        <v>122609130</v>
       </c>
       <c r="B5" t="n">
-        <v>90833</v>
+        <v>91279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521009</v>
+        <v>521075</v>
       </c>
       <c r="R5" t="n">
-        <v>6704113</v>
+        <v>6704005</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609151</v>
+        <v>122609145</v>
       </c>
       <c r="B6" t="n">
-        <v>100506</v>
+        <v>90834</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,35 +1111,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1147,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521159</v>
+        <v>521191</v>
       </c>
       <c r="R6" t="n">
-        <v>6703836</v>
+        <v>6703848</v>
       </c>
       <c r="S6" t="n">
         <v>75</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609122</v>
+        <v>122609097</v>
       </c>
       <c r="B7" t="n">
-        <v>90833</v>
+        <v>90834</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521065</v>
+        <v>521009</v>
       </c>
       <c r="R7" t="n">
-        <v>6704125</v>
+        <v>6704113</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609113</v>
+        <v>122609122</v>
       </c>
       <c r="B8" t="n">
-        <v>91278</v>
+        <v>90834</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521081</v>
+        <v>521065</v>
       </c>
       <c r="R8" t="n">
-        <v>6704102</v>
+        <v>6704125</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1422,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609130</v>
+        <v>122609151</v>
       </c>
       <c r="B9" t="n">
-        <v>91278</v>
+        <v>100507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,30 +1429,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521075</v>
+        <v>521159</v>
       </c>
       <c r="R9" t="n">
-        <v>6704005</v>
+        <v>6703836</v>
       </c>
       <c r="S9" t="n">
         <v>75</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609145</v>
+        <v>122609139</v>
       </c>
       <c r="B10" t="n">
-        <v>90833</v>
+        <v>90834</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521191</v>
+        <v>521067</v>
       </c>
       <c r="R10" t="n">
-        <v>6703848</v>
+        <v>6704010</v>
       </c>
       <c r="S10" t="n">
         <v>75</v>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609047</v>
+        <v>122609113</v>
       </c>
       <c r="B2" t="n">
-        <v>90834</v>
+        <v>91282</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520920</v>
+        <v>521081</v>
       </c>
       <c r="R2" t="n">
-        <v>6704243</v>
+        <v>6704102</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609113</v>
+        <v>122609047</v>
       </c>
       <c r="B3" t="n">
-        <v>91279</v>
+        <v>90837</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521081</v>
+        <v>520920</v>
       </c>
       <c r="R3" t="n">
-        <v>6704102</v>
+        <v>6704243</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609123</v>
+        <v>122609145</v>
       </c>
       <c r="B4" t="n">
-        <v>90834</v>
+        <v>90837</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521094</v>
+        <v>521191</v>
       </c>
       <c r="R4" t="n">
-        <v>6704095</v>
+        <v>6703848</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609130</v>
+        <v>122609151</v>
       </c>
       <c r="B5" t="n">
-        <v>91279</v>
+        <v>100510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,30 +1005,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521075</v>
+        <v>521159</v>
       </c>
       <c r="R5" t="n">
-        <v>6704005</v>
+        <v>6703836</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609145</v>
+        <v>122609139</v>
       </c>
       <c r="B6" t="n">
-        <v>90834</v>
+        <v>90837</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521191</v>
+        <v>521067</v>
       </c>
       <c r="R6" t="n">
-        <v>6703848</v>
+        <v>6704010</v>
       </c>
       <c r="S6" t="n">
         <v>75</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609097</v>
+        <v>122609123</v>
       </c>
       <c r="B7" t="n">
-        <v>90834</v>
+        <v>90837</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521009</v>
+        <v>521094</v>
       </c>
       <c r="R7" t="n">
-        <v>6704113</v>
+        <v>6704095</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609122</v>
+        <v>122609130</v>
       </c>
       <c r="B8" t="n">
-        <v>90834</v>
+        <v>91282</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521065</v>
+        <v>521075</v>
       </c>
       <c r="R8" t="n">
-        <v>6704125</v>
+        <v>6704005</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609151</v>
+        <v>122609097</v>
       </c>
       <c r="B9" t="n">
-        <v>100507</v>
+        <v>90837</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,35 +1434,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521159</v>
+        <v>521009</v>
       </c>
       <c r="R9" t="n">
-        <v>6703836</v>
+        <v>6704113</v>
       </c>
       <c r="S9" t="n">
         <v>75</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609139</v>
+        <v>122609122</v>
       </c>
       <c r="B10" t="n">
-        <v>90834</v>
+        <v>90837</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521067</v>
+        <v>521065</v>
       </c>
       <c r="R10" t="n">
-        <v>6704010</v>
+        <v>6704125</v>
       </c>
       <c r="S10" t="n">
         <v>75</v>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609113</v>
+        <v>122609122</v>
       </c>
       <c r="B2" t="n">
-        <v>91282</v>
+        <v>90837</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521081</v>
+        <v>521065</v>
       </c>
       <c r="R2" t="n">
-        <v>6704102</v>
+        <v>6704125</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609047</v>
+        <v>122609151</v>
       </c>
       <c r="B3" t="n">
-        <v>90837</v>
+        <v>100510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520920</v>
+        <v>521159</v>
       </c>
       <c r="R3" t="n">
-        <v>6704243</v>
+        <v>6703836</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -887,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609145</v>
+        <v>122609097</v>
       </c>
       <c r="B4" t="n">
         <v>90837</v>
@@ -930,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521191</v>
+        <v>521009</v>
       </c>
       <c r="R4" t="n">
-        <v>6703848</v>
+        <v>6704113</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609151</v>
+        <v>122609113</v>
       </c>
       <c r="B5" t="n">
-        <v>100510</v>
+        <v>91282</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,35 +1010,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521159</v>
+        <v>521081</v>
       </c>
       <c r="R5" t="n">
-        <v>6703836</v>
+        <v>6704102</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609130</v>
+        <v>122609145</v>
       </c>
       <c r="B8" t="n">
-        <v>91282</v>
+        <v>90837</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521075</v>
+        <v>521191</v>
       </c>
       <c r="R8" t="n">
-        <v>6704005</v>
+        <v>6703848</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1422,7 +1422,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609097</v>
+        <v>122609047</v>
       </c>
       <c r="B9" t="n">
         <v>90837</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521009</v>
+        <v>520920</v>
       </c>
       <c r="R9" t="n">
-        <v>6704113</v>
+        <v>6704243</v>
       </c>
       <c r="S9" t="n">
         <v>75</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609122</v>
+        <v>122609130</v>
       </c>
       <c r="B10" t="n">
-        <v>90837</v>
+        <v>91282</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521065</v>
+        <v>521075</v>
       </c>
       <c r="R10" t="n">
-        <v>6704125</v>
+        <v>6704005</v>
       </c>
       <c r="S10" t="n">
         <v>75</v>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -1637,7 +1637,7 @@
         <v>122790697</v>
       </c>
       <c r="B11" t="n">
-        <v>100613</v>
+        <v>100621</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>122790687</v>
       </c>
       <c r="B12" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>122790656</v>
       </c>
       <c r="B13" t="n">
-        <v>91385</v>
+        <v>91389</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609145</v>
+        <v>122609151</v>
       </c>
       <c r="B2" t="n">
-        <v>90940</v>
+        <v>100621</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521191</v>
+        <v>521159</v>
       </c>
       <c r="R2" t="n">
-        <v>6703848</v>
+        <v>6703836</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609151</v>
+        <v>122609047</v>
       </c>
       <c r="B3" t="n">
-        <v>100613</v>
+        <v>90944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,35 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521159</v>
+        <v>520920</v>
       </c>
       <c r="R3" t="n">
-        <v>6703836</v>
+        <v>6704243</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -895,7 +895,7 @@
         <v>122609097</v>
       </c>
       <c r="B4" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609123</v>
+        <v>122609145</v>
       </c>
       <c r="B5" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521094</v>
+        <v>521191</v>
       </c>
       <c r="R5" t="n">
-        <v>6704095</v>
+        <v>6703848</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1107,7 +1107,7 @@
         <v>122609113</v>
       </c>
       <c r="B6" t="n">
-        <v>91385</v>
+        <v>91389</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609130</v>
+        <v>122609122</v>
       </c>
       <c r="B7" t="n">
-        <v>91385</v>
+        <v>90944</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521075</v>
+        <v>521065</v>
       </c>
       <c r="R7" t="n">
-        <v>6704005</v>
+        <v>6704125</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609122</v>
+        <v>122609123</v>
       </c>
       <c r="B8" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521065</v>
+        <v>521094</v>
       </c>
       <c r="R8" t="n">
-        <v>6704125</v>
+        <v>6704095</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1425,7 +1425,7 @@
         <v>122609139</v>
       </c>
       <c r="B9" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609047</v>
+        <v>122609130</v>
       </c>
       <c r="B10" t="n">
-        <v>90940</v>
+        <v>91389</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520920</v>
+        <v>521075</v>
       </c>
       <c r="R10" t="n">
-        <v>6704243</v>
+        <v>6704005</v>
       </c>
       <c r="S10" t="n">
         <v>75</v>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609151</v>
+        <v>122609113</v>
       </c>
       <c r="B2" t="n">
-        <v>100621</v>
+        <v>91389</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521159</v>
+        <v>521081</v>
       </c>
       <c r="R2" t="n">
-        <v>6703836</v>
+        <v>6704102</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -786,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609047</v>
+        <v>122609145</v>
       </c>
       <c r="B3" t="n">
         <v>90944</v>
@@ -829,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520920</v>
+        <v>521191</v>
       </c>
       <c r="R3" t="n">
-        <v>6704243</v>
+        <v>6703848</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609097</v>
+        <v>122609151</v>
       </c>
       <c r="B4" t="n">
-        <v>90944</v>
+        <v>100621</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,30 +899,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521009</v>
+        <v>521159</v>
       </c>
       <c r="R4" t="n">
-        <v>6704113</v>
+        <v>6703836</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -998,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609145</v>
+        <v>122609097</v>
       </c>
       <c r="B5" t="n">
         <v>90944</v>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521191</v>
+        <v>521009</v>
       </c>
       <c r="R5" t="n">
-        <v>6703848</v>
+        <v>6704113</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609113</v>
+        <v>122609123</v>
       </c>
       <c r="B6" t="n">
-        <v>91389</v>
+        <v>90944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521081</v>
+        <v>521094</v>
       </c>
       <c r="R6" t="n">
-        <v>6704102</v>
+        <v>6704095</v>
       </c>
       <c r="S6" t="n">
         <v>75</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609122</v>
+        <v>122609139</v>
       </c>
       <c r="B7" t="n">
         <v>90944</v>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521065</v>
+        <v>521067</v>
       </c>
       <c r="R7" t="n">
-        <v>6704125</v>
+        <v>6704010</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1316,7 +1316,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609123</v>
+        <v>122609122</v>
       </c>
       <c r="B8" t="n">
         <v>90944</v>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521094</v>
+        <v>521065</v>
       </c>
       <c r="R8" t="n">
-        <v>6704095</v>
+        <v>6704125</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609139</v>
+        <v>122609130</v>
       </c>
       <c r="B9" t="n">
-        <v>90944</v>
+        <v>91389</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521067</v>
+        <v>521075</v>
       </c>
       <c r="R9" t="n">
-        <v>6704010</v>
+        <v>6704005</v>
       </c>
       <c r="S9" t="n">
         <v>75</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609130</v>
+        <v>122609047</v>
       </c>
       <c r="B10" t="n">
-        <v>91389</v>
+        <v>90944</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521075</v>
+        <v>520920</v>
       </c>
       <c r="R10" t="n">
-        <v>6704005</v>
+        <v>6704243</v>
       </c>
       <c r="S10" t="n">
         <v>75</v>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609113</v>
+        <v>122609122</v>
       </c>
       <c r="B2" t="n">
-        <v>91389</v>
+        <v>90944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521081</v>
+        <v>521065</v>
       </c>
       <c r="R2" t="n">
-        <v>6704102</v>
+        <v>6704125</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609145</v>
+        <v>122609113</v>
       </c>
       <c r="B3" t="n">
-        <v>90944</v>
+        <v>91389</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521191</v>
+        <v>521081</v>
       </c>
       <c r="R3" t="n">
-        <v>6703848</v>
+        <v>6704102</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609151</v>
+        <v>122609145</v>
       </c>
       <c r="B4" t="n">
-        <v>100621</v>
+        <v>90944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,35 +899,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521159</v>
+        <v>521191</v>
       </c>
       <c r="R4" t="n">
-        <v>6703836</v>
+        <v>6703848</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -998,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609097</v>
+        <v>122609047</v>
       </c>
       <c r="B5" t="n">
         <v>90944</v>
@@ -1041,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521009</v>
+        <v>520920</v>
       </c>
       <c r="R5" t="n">
-        <v>6704113</v>
+        <v>6704243</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609139</v>
+        <v>122609151</v>
       </c>
       <c r="B7" t="n">
-        <v>90944</v>
+        <v>100623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,30 +1217,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521067</v>
+        <v>521159</v>
       </c>
       <c r="R7" t="n">
-        <v>6704010</v>
+        <v>6703836</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609122</v>
+        <v>122609130</v>
       </c>
       <c r="B8" t="n">
-        <v>90944</v>
+        <v>91389</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521065</v>
+        <v>521075</v>
       </c>
       <c r="R8" t="n">
-        <v>6704125</v>
+        <v>6704005</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609130</v>
+        <v>122609097</v>
       </c>
       <c r="B9" t="n">
-        <v>91389</v>
+        <v>90944</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521075</v>
+        <v>521009</v>
       </c>
       <c r="R9" t="n">
-        <v>6704005</v>
+        <v>6704113</v>
       </c>
       <c r="S9" t="n">
         <v>75</v>
@@ -1528,7 +1528,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609047</v>
+        <v>122609139</v>
       </c>
       <c r="B10" t="n">
         <v>90944</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520920</v>
+        <v>521067</v>
       </c>
       <c r="R10" t="n">
-        <v>6704243</v>
+        <v>6704010</v>
       </c>
       <c r="S10" t="n">
         <v>75</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122790697</v>
+        <v>122790656</v>
       </c>
       <c r="B11" t="n">
-        <v>100621</v>
+        <v>91389</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,49 +1646,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Matsknutsgårdarna, Dlr</t>
+          <t>Matsknuts gårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521236</v>
+        <v>521119</v>
       </c>
       <c r="R11" t="n">
-        <v>6703806</v>
+        <v>6704030</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1745,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122790687</v>
+        <v>122790697</v>
       </c>
       <c r="B12" t="n">
-        <v>90944</v>
+        <v>100623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,30 +1756,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1788,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521069</v>
+        <v>521236</v>
       </c>
       <c r="R12" t="n">
-        <v>6704232</v>
+        <v>6703806</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1851,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122790656</v>
+        <v>122790687</v>
       </c>
       <c r="B13" t="n">
-        <v>91389</v>
+        <v>90944</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,48 +1867,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Matsknuts gårdarna, Dlr</t>
+          <t>Matsknutsgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521119</v>
+        <v>521069</v>
       </c>
       <c r="R13" t="n">
-        <v>6704030</v>
+        <v>6704232</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609122</v>
+        <v>122609123</v>
       </c>
       <c r="B2" t="n">
         <v>90944</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521065</v>
+        <v>521094</v>
       </c>
       <c r="R2" t="n">
-        <v>6704125</v>
+        <v>6704095</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609113</v>
+        <v>122609097</v>
       </c>
       <c r="B3" t="n">
-        <v>91389</v>
+        <v>90944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521081</v>
+        <v>521009</v>
       </c>
       <c r="R3" t="n">
-        <v>6704102</v>
+        <v>6704113</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609145</v>
+        <v>122609047</v>
       </c>
       <c r="B4" t="n">
         <v>90944</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521191</v>
+        <v>520920</v>
       </c>
       <c r="R4" t="n">
-        <v>6703848</v>
+        <v>6704243</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609047</v>
+        <v>122609145</v>
       </c>
       <c r="B5" t="n">
         <v>90944</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520920</v>
+        <v>521191</v>
       </c>
       <c r="R5" t="n">
-        <v>6704243</v>
+        <v>6703848</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609123</v>
+        <v>122609139</v>
       </c>
       <c r="B6" t="n">
         <v>90944</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521094</v>
+        <v>521067</v>
       </c>
       <c r="R6" t="n">
-        <v>6704095</v>
+        <v>6704010</v>
       </c>
       <c r="S6" t="n">
         <v>75</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609151</v>
+        <v>122609113</v>
       </c>
       <c r="B7" t="n">
-        <v>100623</v>
+        <v>91389</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,35 +1217,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1253,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521159</v>
+        <v>521081</v>
       </c>
       <c r="R7" t="n">
-        <v>6703836</v>
+        <v>6704102</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609130</v>
+        <v>122609151</v>
       </c>
       <c r="B8" t="n">
-        <v>91389</v>
+        <v>100623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,30 +1323,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521075</v>
+        <v>521159</v>
       </c>
       <c r="R8" t="n">
-        <v>6704005</v>
+        <v>6703836</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609097</v>
+        <v>122609130</v>
       </c>
       <c r="B9" t="n">
-        <v>90944</v>
+        <v>91389</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521009</v>
+        <v>521075</v>
       </c>
       <c r="R9" t="n">
-        <v>6704113</v>
+        <v>6704005</v>
       </c>
       <c r="S9" t="n">
         <v>75</v>
@@ -1528,7 +1528,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609139</v>
+        <v>122609122</v>
       </c>
       <c r="B10" t="n">
         <v>90944</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521067</v>
+        <v>521065</v>
       </c>
       <c r="R10" t="n">
-        <v>6704010</v>
+        <v>6704125</v>
       </c>
       <c r="S10" t="n">
         <v>75</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122790656</v>
+        <v>122790697</v>
       </c>
       <c r="B11" t="n">
-        <v>91389</v>
+        <v>100623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,48 +1646,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Matsknuts gårdarna, Dlr</t>
+          <t>Matsknutsgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521119</v>
+        <v>521236</v>
       </c>
       <c r="R11" t="n">
-        <v>6704030</v>
+        <v>6703806</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122790697</v>
+        <v>122790656</v>
       </c>
       <c r="B12" t="n">
-        <v>100623</v>
+        <v>91389</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,49 +1757,48 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Matsknutsgårdarna, Dlr</t>
+          <t>Matsknuts gårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521236</v>
+        <v>521119</v>
       </c>
       <c r="R12" t="n">
-        <v>6703806</v>
+        <v>6704030</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609123</v>
+        <v>122609113</v>
       </c>
       <c r="B2" t="n">
-        <v>90944</v>
+        <v>91397</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521094</v>
+        <v>521081</v>
       </c>
       <c r="R2" t="n">
-        <v>6704095</v>
+        <v>6704102</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609097</v>
+        <v>122609047</v>
       </c>
       <c r="B3" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521009</v>
+        <v>520920</v>
       </c>
       <c r="R3" t="n">
-        <v>6704113</v>
+        <v>6704243</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609047</v>
+        <v>122609130</v>
       </c>
       <c r="B4" t="n">
-        <v>90944</v>
+        <v>91397</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520920</v>
+        <v>521075</v>
       </c>
       <c r="R4" t="n">
-        <v>6704243</v>
+        <v>6704005</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609145</v>
+        <v>122609151</v>
       </c>
       <c r="B5" t="n">
-        <v>90944</v>
+        <v>100631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,30 +1005,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521191</v>
+        <v>521159</v>
       </c>
       <c r="R5" t="n">
-        <v>6703848</v>
+        <v>6703836</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609139</v>
+        <v>122609097</v>
       </c>
       <c r="B6" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521067</v>
+        <v>521009</v>
       </c>
       <c r="R6" t="n">
-        <v>6704010</v>
+        <v>6704113</v>
       </c>
       <c r="S6" t="n">
         <v>75</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609113</v>
+        <v>122609139</v>
       </c>
       <c r="B7" t="n">
-        <v>91389</v>
+        <v>90952</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521081</v>
+        <v>521067</v>
       </c>
       <c r="R7" t="n">
-        <v>6704102</v>
+        <v>6704010</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609151</v>
+        <v>122609122</v>
       </c>
       <c r="B8" t="n">
-        <v>100623</v>
+        <v>90952</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,35 +1328,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521159</v>
+        <v>521065</v>
       </c>
       <c r="R8" t="n">
-        <v>6703836</v>
+        <v>6704125</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609130</v>
+        <v>122609123</v>
       </c>
       <c r="B9" t="n">
-        <v>91389</v>
+        <v>90952</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521075</v>
+        <v>521094</v>
       </c>
       <c r="R9" t="n">
-        <v>6704005</v>
+        <v>6704095</v>
       </c>
       <c r="S9" t="n">
         <v>75</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609122</v>
+        <v>122609145</v>
       </c>
       <c r="B10" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521065</v>
+        <v>521191</v>
       </c>
       <c r="R10" t="n">
-        <v>6704125</v>
+        <v>6703848</v>
       </c>
       <c r="S10" t="n">
         <v>75</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122790697</v>
+        <v>122790656</v>
       </c>
       <c r="B11" t="n">
-        <v>100623</v>
+        <v>91397</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,49 +1646,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Matsknutsgårdarna, Dlr</t>
+          <t>Matsknuts gårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521236</v>
+        <v>521119</v>
       </c>
       <c r="R11" t="n">
-        <v>6703806</v>
+        <v>6704030</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1745,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122790656</v>
+        <v>122790697</v>
       </c>
       <c r="B12" t="n">
-        <v>91389</v>
+        <v>100631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,48 +1756,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Matsknuts gårdarna, Dlr</t>
+          <t>Matsknutsgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521119</v>
+        <v>521236</v>
       </c>
       <c r="R12" t="n">
-        <v>6704030</v>
+        <v>6703806</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>122790687</v>
       </c>
       <c r="B13" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609113</v>
+        <v>122609123</v>
       </c>
       <c r="B2" t="n">
-        <v>91397</v>
+        <v>90952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521081</v>
+        <v>521094</v>
       </c>
       <c r="R2" t="n">
-        <v>6704102</v>
+        <v>6704095</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609047</v>
+        <v>122609130</v>
       </c>
       <c r="B3" t="n">
-        <v>90952</v>
+        <v>91397</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520920</v>
+        <v>521075</v>
       </c>
       <c r="R3" t="n">
-        <v>6704243</v>
+        <v>6704005</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609130</v>
+        <v>122609151</v>
       </c>
       <c r="B4" t="n">
-        <v>91397</v>
+        <v>100631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,30 +899,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521075</v>
+        <v>521159</v>
       </c>
       <c r="R4" t="n">
-        <v>6704005</v>
+        <v>6703836</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122609151</v>
+        <v>122609122</v>
       </c>
       <c r="B5" t="n">
-        <v>100631</v>
+        <v>90952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,35 +1010,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521159</v>
+        <v>521065</v>
       </c>
       <c r="R5" t="n">
-        <v>6703836</v>
+        <v>6704125</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609097</v>
+        <v>122609145</v>
       </c>
       <c r="B6" t="n">
         <v>90952</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521009</v>
+        <v>521191</v>
       </c>
       <c r="R6" t="n">
-        <v>6704113</v>
+        <v>6703848</v>
       </c>
       <c r="S6" t="n">
         <v>75</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609139</v>
+        <v>122609047</v>
       </c>
       <c r="B7" t="n">
         <v>90952</v>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521067</v>
+        <v>520920</v>
       </c>
       <c r="R7" t="n">
-        <v>6704010</v>
+        <v>6704243</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1316,7 +1316,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609122</v>
+        <v>122609139</v>
       </c>
       <c r="B8" t="n">
         <v>90952</v>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521065</v>
+        <v>521067</v>
       </c>
       <c r="R8" t="n">
-        <v>6704125</v>
+        <v>6704010</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609123</v>
+        <v>122609113</v>
       </c>
       <c r="B9" t="n">
-        <v>90952</v>
+        <v>91397</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521094</v>
+        <v>521081</v>
       </c>
       <c r="R9" t="n">
-        <v>6704095</v>
+        <v>6704102</v>
       </c>
       <c r="S9" t="n">
         <v>75</v>
@@ -1528,7 +1528,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609145</v>
+        <v>122609097</v>
       </c>
       <c r="B10" t="n">
         <v>90952</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521191</v>
+        <v>521009</v>
       </c>
       <c r="R10" t="n">
-        <v>6703848</v>
+        <v>6704113</v>
       </c>
       <c r="S10" t="n">
         <v>75</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122790656</v>
+        <v>122790687</v>
       </c>
       <c r="B11" t="n">
-        <v>91397</v>
+        <v>90952</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,48 +1646,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Matsknuts gårdarna, Dlr</t>
+          <t>Matsknutsgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521119</v>
+        <v>521069</v>
       </c>
       <c r="R11" t="n">
-        <v>6704030</v>
+        <v>6704232</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122790697</v>
+        <v>122790656</v>
       </c>
       <c r="B12" t="n">
-        <v>100631</v>
+        <v>91397</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,49 +1752,48 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Matsknutsgårdarna, Dlr</t>
+          <t>Matsknuts gårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521236</v>
+        <v>521119</v>
       </c>
       <c r="R12" t="n">
-        <v>6703806</v>
+        <v>6704030</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1855,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122790687</v>
+        <v>122790697</v>
       </c>
       <c r="B13" t="n">
-        <v>90952</v>
+        <v>100631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,30 +1862,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521069</v>
+        <v>521236</v>
       </c>
       <c r="R13" t="n">
-        <v>6704232</v>
+        <v>6703806</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122790687</v>
+        <v>122790656</v>
       </c>
       <c r="B11" t="n">
-        <v>90952</v>
+        <v>91397</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,44 +1646,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Matsknutsgårdarna, Dlr</t>
+          <t>Matsknuts gårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521069</v>
+        <v>521119</v>
       </c>
       <c r="R11" t="n">
-        <v>6704232</v>
+        <v>6704030</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122790656</v>
+        <v>122790697</v>
       </c>
       <c r="B12" t="n">
-        <v>91397</v>
+        <v>100631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,48 +1756,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Matsknuts gårdarna, Dlr</t>
+          <t>Matsknutsgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521119</v>
+        <v>521236</v>
       </c>
       <c r="R12" t="n">
-        <v>6704030</v>
+        <v>6703806</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1850,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122790697</v>
+        <v>122790687</v>
       </c>
       <c r="B13" t="n">
-        <v>100631</v>
+        <v>90952</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,35 +1867,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521236</v>
+        <v>521069</v>
       </c>
       <c r="R13" t="n">
-        <v>6703806</v>
+        <v>6704232</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122790656</v>
+        <v>122790687</v>
       </c>
       <c r="B11" t="n">
-        <v>91397</v>
+        <v>90955</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,48 +1646,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Matsknuts gårdarna, Dlr</t>
+          <t>Matsknutsgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521119</v>
+        <v>521069</v>
       </c>
       <c r="R11" t="n">
-        <v>6704030</v>
+        <v>6704232</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1747,7 +1743,7 @@
         <v>122790697</v>
       </c>
       <c r="B12" t="n">
-        <v>100631</v>
+        <v>100634</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122790687</v>
+        <v>122790656</v>
       </c>
       <c r="B13" t="n">
-        <v>90952</v>
+        <v>91400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,44 +1863,48 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Matsknutsgårdarna, Dlr</t>
+          <t>Matsknuts gårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521069</v>
+        <v>521119</v>
       </c>
       <c r="R13" t="n">
-        <v>6704232</v>
+        <v>6704030</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122790687</v>
+        <v>122790656</v>
       </c>
       <c r="B11" t="n">
-        <v>90955</v>
+        <v>91402</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,44 +1646,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Matsknutsgårdarna, Dlr</t>
+          <t>Matsknuts gårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521069</v>
+        <v>521119</v>
       </c>
       <c r="R11" t="n">
-        <v>6704232</v>
+        <v>6704030</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,7 +1747,7 @@
         <v>122790697</v>
       </c>
       <c r="B12" t="n">
-        <v>100634</v>
+        <v>100636</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122790656</v>
+        <v>122790687</v>
       </c>
       <c r="B13" t="n">
-        <v>91400</v>
+        <v>90957</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,48 +1867,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Matsknuts gårdarna, Dlr</t>
+          <t>Matsknutsgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521119</v>
+        <v>521069</v>
       </c>
       <c r="R13" t="n">
-        <v>6704030</v>
+        <v>6704232</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122790656</v>
+        <v>122790687</v>
       </c>
       <c r="B11" t="n">
-        <v>91402</v>
+        <v>90963</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,48 +1646,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Matsknuts gårdarna, Dlr</t>
+          <t>Matsknutsgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521119</v>
+        <v>521069</v>
       </c>
       <c r="R11" t="n">
-        <v>6704030</v>
+        <v>6704232</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1747,7 +1743,7 @@
         <v>122790697</v>
       </c>
       <c r="B12" t="n">
-        <v>100636</v>
+        <v>100642</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122790687</v>
+        <v>122790656</v>
       </c>
       <c r="B13" t="n">
-        <v>90957</v>
+        <v>91408</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,44 +1863,48 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Matsknutsgårdarna, Dlr</t>
+          <t>Matsknuts gårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521069</v>
+        <v>521119</v>
       </c>
       <c r="R13" t="n">
-        <v>6704232</v>
+        <v>6704030</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1959,6 +1959,103 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129662951</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91851</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>658</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>kalles väg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>521067</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6704019</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -1964,7 +1964,7 @@
         <v>129662951</v>
       </c>
       <c r="B14" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -1964,7 +1964,7 @@
         <v>129662951</v>
       </c>
       <c r="B14" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -1964,7 +1964,7 @@
         <v>129662951</v>
       </c>
       <c r="B14" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -1964,7 +1964,7 @@
         <v>129662951</v>
       </c>
       <c r="B14" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -1964,7 +1964,7 @@
         <v>129662951</v>
       </c>
       <c r="B14" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -1964,7 +1964,7 @@
         <v>129662951</v>
       </c>
       <c r="B14" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -1964,7 +1964,7 @@
         <v>129662951</v>
       </c>
       <c r="B14" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -1964,7 +1964,7 @@
         <v>129662951</v>
       </c>
       <c r="B14" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -1964,7 +1964,7 @@
         <v>129662951</v>
       </c>
       <c r="B14" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122609123</v>
+        <v>129662951</v>
       </c>
       <c r="B2" t="n">
-        <v>90952</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Matsknutsgårdarna, Dlr</t>
+          <t>kalles väg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521094</v>
+        <v>521067</v>
       </c>
       <c r="R2" t="n">
-        <v>6704095</v>
+        <v>6704019</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,56 +754,50 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122609130</v>
+        <v>122609047</v>
       </c>
       <c r="B3" t="n">
-        <v>91397</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521075</v>
+        <v>520920</v>
       </c>
       <c r="R3" t="n">
-        <v>6704005</v>
+        <v>6704243</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -887,47 +873,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122609151</v>
+        <v>122609097</v>
       </c>
       <c r="B4" t="n">
-        <v>100631</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +911,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521159</v>
+        <v>521009</v>
       </c>
       <c r="R4" t="n">
-        <v>6703836</v>
+        <v>6704113</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -1001,12 +977,7 @@
         <v>122609122</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,15 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122609145</v>
+        <v>122609123</v>
       </c>
       <c r="B6" t="n">
-        <v>90952</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521191</v>
+        <v>521094</v>
       </c>
       <c r="R6" t="n">
-        <v>6703848</v>
+        <v>6704095</v>
       </c>
       <c r="S6" t="n">
         <v>75</v>
@@ -1210,15 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122609047</v>
+        <v>122609139</v>
       </c>
       <c r="B7" t="n">
-        <v>90952</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520920</v>
+        <v>521067</v>
       </c>
       <c r="R7" t="n">
-        <v>6704243</v>
+        <v>6704010</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1316,15 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122609139</v>
+        <v>122609145</v>
       </c>
       <c r="B8" t="n">
-        <v>90952</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,10 +1315,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521067</v>
+        <v>521191</v>
       </c>
       <c r="R8" t="n">
-        <v>6704010</v>
+        <v>6703848</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1422,37 +1378,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122609113</v>
+        <v>122790687</v>
       </c>
       <c r="B9" t="n">
-        <v>91397</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1465,13 +1416,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521081</v>
+        <v>521069</v>
       </c>
       <c r="R9" t="n">
-        <v>6704102</v>
+        <v>6704232</v>
       </c>
       <c r="S9" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,12 +1446,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,15 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122609097</v>
+        <v>122609113</v>
       </c>
       <c r="B10" t="n">
-        <v>90952</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,21 +1490,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1517,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521009</v>
+        <v>521081</v>
       </c>
       <c r="R10" t="n">
-        <v>6704113</v>
+        <v>6704102</v>
       </c>
       <c r="S10" t="n">
         <v>75</v>
@@ -1634,15 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122790687</v>
+        <v>122609130</v>
       </c>
       <c r="B11" t="n">
-        <v>90966</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,21 +1591,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,13 +1618,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521069</v>
+        <v>521075</v>
       </c>
       <c r="R11" t="n">
-        <v>6704232</v>
+        <v>6704005</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1707,12 +1648,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,61 +1681,55 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122790697</v>
+        <v>122790656</v>
       </c>
       <c r="B12" t="n">
-        <v>100645</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Matsknutsgårdarna, Dlr</t>
+          <t>Matsknuts gårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521236</v>
+        <v>521119</v>
       </c>
       <c r="R12" t="n">
-        <v>6703806</v>
+        <v>6704030</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,60 +1786,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122790656</v>
+        <v>122609151</v>
       </c>
       <c r="B13" t="n">
-        <v>91411</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Matsknuts gårdarna, Dlr</t>
+          <t>Matsknutsgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521119</v>
+        <v>521159</v>
       </c>
       <c r="R13" t="n">
-        <v>6704030</v>
+        <v>6703836</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1928,12 +1859,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1961,48 +1892,56 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129662951</v>
+        <v>122790697</v>
       </c>
       <c r="B14" t="n">
-        <v>91904</v>
+        <v>101326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>kalles väg, Dlr</t>
+          <t>Matsknutsgårdarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521067</v>
+        <v>521236</v>
       </c>
       <c r="R14" t="n">
-        <v>6704019</v>
+        <v>6703806</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2026,12 +1965,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2040,18 +1979,19 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 3087-2025 artfynd.xlsx
+++ b/artfynd/A 3087-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129662951</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122609047</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122609097</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122609122</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122609123</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122609139</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122609145</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122790687</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122609113</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122609130</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122790656</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122609151</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1995,8 +2060,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122790697</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>